--- a/wooclap/imports/optional/03_Search_Part_1_optional.xlsx
+++ b/wooclap/imports/optional/03_Search_Part_1_optional.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$2</definedName>

--- a/wooclap/imports/optional/03_Search_Part_1_optional.xlsx
+++ b/wooclap/imports/optional/03_Search_Part_1_optional.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L01-O02 · A robot can move A → B → A. If it never checks where it has already been, what problem could occur?</t>
+          <t>L01-O02 · The only directed edges are S→A, S→B, A→X and B→X. A search rejects a child only if its state already appears on that same path; it has no global visited set. What happens to S→A→X and S→B→X?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -527,22 +527,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>It must reach every goal immediately.</t>
+          <t>The second path is rejected as a cycle because X was reached on the first path.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The two locations automatically become one location.</t>
+          <t>Both paths are rejected because a state may have only one parent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>It could keep going around the same loop.</t>
+          <t>Both paths are kept: neither contains a cycle, though both end at X.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The robot can never return to A.</t>
+          <t>The second path is automatically merged with the first by the path cycle check.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
